--- a/microbit-program/autumn-2026/quiz/kahoot-import/week-02-da.xlsx
+++ b/microbit-program/autumn-2026/quiz/kahoot-import/week-02-da.xlsx
@@ -456,60 +456,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hvor mange lys (LED) er der på micro:bit'ens forside?</t>
+          <t>Hvilken blok gentager koden igen og igen for evigt?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>on start</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>show number</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>pause</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>forever</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hvad hedder de to knapper på micro:bit'en?</t>
+          <t>Hvilken blok viser et lille billede som et hjerte eller et ansigt?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A og B</t>
+          <t>show icon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1 og 2</t>
+          <t>show string</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>X og Y</t>
+          <t>radio send</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Op og Ned</t>
+          <t>show number</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -522,126 +522,126 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hvilken blok gentager koden HELE tiden, igen og igen?</t>
+          <t>Hvad gør blokken 'pause (ms)'?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>forever</t>
+          <t>Genstarter boardet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>on start</t>
+          <t>Tænder for musikken</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pause</t>
+          <t>Får programmet til at vente lidt</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>show number</t>
+          <t>Sletter al koden</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hvilken blok bruger du til at vise et hjerte?</t>
+          <t>Hvilken blok viser bogstaver og ord?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>show icon</t>
+          <t>show arrow</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>pause</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>show number</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>show string</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>pause</t>
-        </is>
-      </c>
       <c r="F5" t="n">
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hvad gør blokken 'pause (ms)'?</t>
+          <t>Hvad hedder det gratis website, hvor vi bygger koden?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Venter et lille øjeblik</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sletter skærmen</t>
+          <t>Google Docs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Spiller en sang</t>
+          <t>Minecraft</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Viser dit navn</t>
+          <t>MakeCode</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hvor koder man til micro:bit'en?</t>
+          <t>Hvad sker der, når du trykker på ▶️-knappen i MakeCode?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>makecode.microbit.org</t>
+          <t>Programmet kører i simulatoren</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Computeren slukker</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paint</t>
+          <t>Koden slettes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Der printes</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -654,93 +654,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hvordan får du dit program over på det rigtige board?</t>
+          <t>Hvilken blok kører, når du trykker på knap A?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Download .hex og træk til MICROBIT</t>
+          <t>forever</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Print det på papir</t>
+          <t>on button A pressed</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Send en SMS</t>
+          <t>on shake</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tag et billede</t>
+          <t>on start</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hvilken blok viser bogstaver og ord?</t>
+          <t>Hvad gør blokken 'show leds'?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>show string</t>
+          <t>Sender en besked</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>show number</t>
+          <t>Tænder præcis de lys, du vælger</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>show leds</t>
+          <t>Viser et tal</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>pause</t>
+          <t>Spiller en sang</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hjertet skal banke HURTIGERE. Hvad gør du?</t>
+          <t>Hvordan laver man et hjerte, der 'banker'?</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gør pausen kortere</t>
+          <t>Skift mellem stort og lille hjerte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gør pausen længere</t>
+          <t>Ryst boardet</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fjern forever</t>
+          <t>Sluk lyset</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sluk boardet</t>
+          <t>Tryk på A hele tiden</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -753,40 +753,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hvilket ikon er det MINDSTE hjerte?</t>
+          <t>Hvilken bevægelse kan micro:bit'en mærke helt af sig selv?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Small heart</t>
+          <t>Din alder</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Heart</t>
+          <t>Rystelse (shake)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Duck</t>
+          <t>Din yndlingsret</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Din stemmes farve</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>🎮 Hvilket spil handler om at bygge med firkantede klodser?</t>
+          <t>🎮 I hvilket spil bygger man næsten alt med firkantede klodser?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mario Kart</t>
+          <t>Tetris</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tetris</t>
+          <t>Wordle</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -819,133 +819,133 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>🎉 Hvad råber alle efter 'six...'?</t>
+          <t>🎉 Hvilket tal kommer efter 'six...' i den kendte trend?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>seven!</t>
+          <t>ten</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>eight!</t>
+          <t>four</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>nine!</t>
+          <t>seven</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ten!</t>
+          <t>tolv</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>🕹️ Hvor laver man 'obbys' og sine egne mini-spil?</t>
+          <t>🕹️ Hvor laver folk deres egne spil og 'obbys'?</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Zoom</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Roblox</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Snake</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Pac-Man</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kabale</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>😹 Hvad er en 'meme'?</t>
+          <t>😹 Hvad kalder man et sjovt billede eller klip, der spredes på nettet?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Et sjovt billede/video man deler</t>
+          <t>En pause</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>En slags kage</t>
+          <t>En pixel</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>En micro:bit-blok</t>
+          <t>En meme</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>En knap</t>
+          <t>En variabel</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>📱 'Skibidi' blev kæmpestort på hvilke apps?</t>
+          <t>📱 'Skibidi' blev mega-populært især på hvilke apps?</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Paint</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>YouTube og TikTok</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Word</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paint</t>
+          <t>Lommeregner</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/microbit-program/autumn-2026/quiz/kahoot-import/week-02-da.xlsx
+++ b/microbit-program/autumn-2026/quiz/kahoot-import/week-02-da.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>on start</t>
+          <t>ved start</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>show number</t>
+          <t>vis tal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pause</t>
+          <t>pause (ms)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>forever</t>
+          <t>gentag for altid</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -494,12 +494,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>show icon</t>
+          <t>vis ikon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>show string</t>
+          <t>vis tekst</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>show number</t>
+          <t>vis tal</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -560,22 +560,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>show arrow</t>
+          <t>vis pil</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pause</t>
+          <t>pause (ms)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>show number</t>
+          <t>vis tal</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>show string</t>
+          <t>vis tekst</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Der printes</t>
+          <t>Der printes på papir</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,22 +659,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>forever</t>
+          <t>gentag for altid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>on button A pressed</t>
+          <t>da knap A trykkes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>on shake</t>
+          <t>da rystet</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>on start</t>
+          <t>ved start</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -687,7 +687,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hvad gør blokken 'show leds'?</t>
+          <t>Hvad gør blokken 'vis lys' (show leds)?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ten</t>
+          <t>ti</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>four</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>seven</t>
+          <t>syv</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lommeregner</t>
+          <t>Lommeregneren</t>
         </is>
       </c>
       <c r="F16" t="n">

--- a/microbit-program/autumn-2026/quiz/kahoot-import/week-02-da.xlsx
+++ b/microbit-program/autumn-2026/quiz/kahoot-import/week-02-da.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ved start</t>
+          <t>når programmet starter</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vis tal</t>
+          <t>vis nummer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>gentag for altid</t>
+          <t>for altid</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -499,17 +499,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vis tekst</t>
+          <t>vis streng</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>radio send</t>
+          <t>radio send nummer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>vis tal</t>
+          <t>vis nummer</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -570,12 +570,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>vis tal</t>
+          <t>vis nummer</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>vis tekst</t>
+          <t>vis streng</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -659,22 +659,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gentag for altid</t>
+          <t>for altid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>da knap A trykkes</t>
+          <t>når der trykkes på knappen A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>da rystet</t>
+          <t>på ryst</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ved start</t>
+          <t>når programmet starter</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -687,7 +687,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hvad gør blokken 'vis lys' (show leds)?</t>
+          <t>Hvad gør blokken 'vis LED'er' (show leds)?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
